--- a/data/LLMSurveys_Configurations.xlsx
+++ b/data/LLMSurveys_Configurations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Current\Work\LLMExpectations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80B1D39-22AF-42A8-8E56-C90E9004F481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4319C4-6D63-47F7-9D95-C5B615CBFAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1E49B1B9-B097-4895-90AA-09F755188166}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="29">
   <si>
     <t>UsdRub</t>
   </si>
@@ -115,13 +115,19 @@
   </si>
   <si>
     <t>QWEN 3.8 (все данные + IE - markers, -7d от Инфом)</t>
+  </si>
+  <si>
+    <t>QWEN 3.6 (только RLMS, -7d от Инфом)</t>
+  </si>
+  <si>
+    <t>QWEN 3.8 (+RLMS full  -news +reg inf, 7d)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +146,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6AAB73"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -149,35 +161,11 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -196,65 +184,45 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -585,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF250728-16E4-438D-A8DD-F8C642EF43D3}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="55.81640625" customWidth="1"/>
@@ -593,28 +561,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -622,519 +591,591 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="5" t="s">
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="5" t="s">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="5" t="s">
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="5" t="s">
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="5" t="s">
+      <c r="B15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="4" t="s">
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="4" t="s">
+      <c r="B17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:J17">
+  <conditionalFormatting sqref="B1:J18">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"Да"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>"Нет"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:J19">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Да"</formula>
     </cfRule>

--- a/data/LLMSurveys_Configurations.xlsx
+++ b/data/LLMSurveys_Configurations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Current\Work\LLMExpectations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4319C4-6D63-47F7-9D95-C5B615CBFAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A0A61E-D680-43B3-8352-EC29AFFDB7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1E49B1B9-B097-4895-90AA-09F755188166}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E49B1B9-B097-4895-90AA-09F755188166}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="30">
   <si>
     <t>UsdRub</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>QWEN 3.8 (+RLMS full  -news +reg inf, 7d)</t>
+  </si>
+  <si>
+    <t>mlcluster_qwen38_async_no_news_rlms_e_reginf_-6d</t>
   </si>
 </sst>
 </file>
@@ -553,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF250728-16E4-438D-A8DD-F8C642EF43D3}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="55.81640625" customWidth="1"/>
@@ -1166,8 +1169,40 @@
         <v>10</v>
       </c>
     </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:J18">
+  <conditionalFormatting sqref="B1:J19">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"Да"</formula>
     </cfRule>
@@ -1175,7 +1210,7 @@
       <formula>"Нет"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:J19">
+  <conditionalFormatting sqref="B20:J20">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Да"</formula>
     </cfRule>

--- a/data/LLMSurveys_Configurations.xlsx
+++ b/data/LLMSurveys_Configurations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Current\Work\LLMExpectations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A0A61E-D680-43B3-8352-EC29AFFDB7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E67C3F-1D20-4911-9701-08B35806BCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E49B1B9-B097-4895-90AA-09F755188166}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="31">
   <si>
     <t>UsdRub</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>mlcluster_qwen38_async_no_news_rlms_e_reginf_-6d</t>
+  </si>
+  <si>
+    <t>Anews</t>
   </si>
 </sst>
 </file>
@@ -205,27 +208,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -556,14 +539,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF250728-16E4-438D-A8DD-F8C642EF43D3}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="55.81640625" customWidth="1"/>
-    <col min="11" max="11" width="28.81640625" customWidth="1"/>
+    <col min="12" max="12" width="28.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -572,28 +555,31 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -604,19 +590,19 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>9</v>
@@ -624,8 +610,11 @@
       <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -636,10 +625,10 @@
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>10</v>
@@ -656,8 +645,11 @@
       <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -668,13 +660,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>10</v>
@@ -686,10 +678,13 @@
         <v>10</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>10</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -700,28 +695,31 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -732,13 +730,13 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>10</v>
@@ -752,8 +750,11 @@
       <c r="J6" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -764,7 +765,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>9</v>
@@ -776,7 +777,7 @@
         <v>9</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>10</v>
@@ -784,8 +785,11 @@
       <c r="J7" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -796,7 +800,7 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>9</v>
@@ -811,13 +815,16 @@
         <v>9</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -828,7 +835,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>9</v>
@@ -843,13 +850,16 @@
         <v>9</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
@@ -860,7 +870,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
@@ -872,7 +882,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>10</v>
@@ -880,8 +890,11 @@
       <c r="J10" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
@@ -892,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>9</v>
@@ -904,16 +917,19 @@
         <v>9</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -924,28 +940,31 @@
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
@@ -956,28 +975,31 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
@@ -988,19 +1010,19 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>10</v>
@@ -1008,8 +1030,11 @@
       <c r="J14" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="3" t="s">
         <v>23</v>
       </c>
@@ -1020,13 +1045,13 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>10</v>
@@ -1035,13 +1060,16 @@
         <v>10</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
@@ -1055,10 +1083,10 @@
         <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>10</v>
@@ -1067,13 +1095,16 @@
         <v>10</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
@@ -1087,25 +1118,28 @@
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1128,16 +1162,19 @@
         <v>10</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="4" t="s">
         <v>28</v>
       </c>
@@ -1151,25 +1188,28 @@
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>9</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="4" t="s">
         <v>29</v>
       </c>
@@ -1183,10 +1223,10 @@
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>10</v>
@@ -1195,22 +1235,17 @@
         <v>10</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:J19">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"Да"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>"Нет"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20:J20">
+  <conditionalFormatting sqref="B1:K20">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Да"</formula>
     </cfRule>

--- a/data/LLMSurveys_Configurations.xlsx
+++ b/data/LLMSurveys_Configurations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Current\Work\LLMExpectations\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E67C3F-1D20-4911-9701-08B35806BCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE79FFC-F114-4585-8DBA-406AA1886370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E49B1B9-B097-4895-90AA-09F755188166}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1E49B1B9-B097-4895-90AA-09F755188166}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="32">
   <si>
     <t>UsdRub</t>
   </si>
@@ -123,10 +123,13 @@
     <t>QWEN 3.8 (+RLMS full  -news +reg inf, 7d)</t>
   </si>
   <si>
-    <t>mlcluster_qwen38_async_no_news_rlms_e_reginf_-6d</t>
-  </si>
-  <si>
     <t>Anews</t>
+  </si>
+  <si>
+    <t>QWEN 3.8 (+RLMS e  -news +reg inf, 7d)</t>
+  </si>
+  <si>
+    <t>QWEN 3.8 (+RLMS full  +anews +reg inf, 7d)</t>
   </si>
 </sst>
 </file>
@@ -208,7 +211,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -539,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF250728-16E4-438D-A8DD-F8C642EF43D3}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="55.81640625" customWidth="1"/>
@@ -555,7 +578,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -1211,7 +1234,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>10</v>
@@ -1241,11 +1264,54 @@
         <v>9</v>
       </c>
       <c r="K20" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:K20">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"Да"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>"Нет"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:K21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Да"</formula>
     </cfRule>
@@ -1254,5 +1320,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/LLMSurveys_Configurations.xlsx
+++ b/data/LLMSurveys_Configurations.xlsx
@@ -211,27 +211,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1303,15 +1283,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:K20">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"Да"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>"Нет"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21:K21">
+  <conditionalFormatting sqref="B1:K21">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Да"</formula>
     </cfRule>
